--- a/엑셀양식/최종목차_탭_양식.xlsx
+++ b/엑셀양식/최종목차_탭_양식.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>확정 / 검토 중 / 초안 / 보류 / 제외 — ‘제외’ 행은 목차에서 빠지고 ‘실습 목차에서 뺀 아이디어’에 비고(이유)와 함께 표시</t>
+          <t>확정 / 검토 중 / 초안 / 가안 / 보류 / 재검토 — ‘재검토’ 행은 목차에서 빠지고 ‘재검토 아이디어’에 비고(이유)와 함께 표시</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       <formula1>"수업자동화,업무자동화"</formula1>
     </dataValidation>
     <dataValidation sqref="I11:I70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"확정,검토 중,초안,보류,제외"</formula1>
+      <formula1>"확정,검토 중,초안,가안,보류,재검토"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/엑셀양식/최종목차_탭_양식.xlsx
+++ b/엑셀양식/최종목차_탭_양식.xlsx
@@ -484,19 +484,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,34 +546,46 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>세부 내용</t>
+          <t>파트 설명</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>꼭지 아래에 보일 항목. 한 칸 안에서 줄을 바꿔(Alt+Enter) 하나씩 적기</t>
+          <t>PART 제목 아래에 보일 설명(사용 도구 등). 그 파트의 첫 꼭지 행에만 적으면 됨</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>바탕 아이디어 번호</t>
+          <t>세부 내용</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>같은 권의 아이디어 번호를 쉼표로 (예: 21, 22). 다른 권 아이디어는 '수업 14', '업무 7'처럼</t>
+          <t>꼭지 아래에 보일 항목. 한 칸 안에서 줄을 바꿔(Alt+Enter) 하나씩 적기</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>바탕 아이디어 번호</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>같은 권의 아이디어 번호를 쉼표로 (예: 21, 22). 다른 권 아이디어는 '수업 14', '업무 7'처럼</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>확정 / 검토 중 / 초안 / 가안 / 보류 / 재검토 — ‘재검토’ 행은 목차에서 빠지고 ‘재검토 아이디어’에 비고(이유)와 함께 표시</t>
         </is>
@@ -596,35 +609,40 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>파트 설명</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
           <t>꼭지 번호</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>꼭지 제목</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>세부 내용</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>바탕 아이디어 번호</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>저자</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -647,764 +665,826 @@
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>프롬프트 기초</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>프롬프트가 결과를 좌우한다
 마크다운 기초</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>검토 중</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="6" t="n"/>
       <c r="F11" s="7" t="n"/>
-      <c r="G11" s="6" t="n"/>
+      <c r="G11" s="7" t="n"/>
       <c r="H11" s="6" t="n"/>
       <c r="I11" s="6" t="n"/>
-      <c r="J11" s="7" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="6" t="n"/>
       <c r="F12" s="7" t="n"/>
-      <c r="G12" s="6" t="n"/>
+      <c r="G12" s="7" t="n"/>
       <c r="H12" s="6" t="n"/>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="7" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="6" t="n"/>
       <c r="F13" s="7" t="n"/>
-      <c r="G13" s="6" t="n"/>
+      <c r="G13" s="7" t="n"/>
       <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="7" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="6" t="n"/>
       <c r="F14" s="7" t="n"/>
-      <c r="G14" s="6" t="n"/>
+      <c r="G14" s="7" t="n"/>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="7" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="7" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="6" t="n"/>
       <c r="F15" s="7" t="n"/>
-      <c r="G15" s="6" t="n"/>
+      <c r="G15" s="7" t="n"/>
       <c r="H15" s="6" t="n"/>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="7" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="6" t="n"/>
       <c r="F16" s="7" t="n"/>
-      <c r="G16" s="6" t="n"/>
+      <c r="G16" s="7" t="n"/>
       <c r="H16" s="6" t="n"/>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="7" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="6" t="n"/>
       <c r="F17" s="7" t="n"/>
-      <c r="G17" s="6" t="n"/>
+      <c r="G17" s="7" t="n"/>
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="7" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="6" t="n"/>
       <c r="F18" s="7" t="n"/>
-      <c r="G18" s="6" t="n"/>
+      <c r="G18" s="7" t="n"/>
       <c r="H18" s="6" t="n"/>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="7" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="6" t="n"/>
       <c r="F19" s="7" t="n"/>
-      <c r="G19" s="6" t="n"/>
+      <c r="G19" s="7" t="n"/>
       <c r="H19" s="6" t="n"/>
       <c r="I19" s="6" t="n"/>
-      <c r="J19" s="7" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="6" t="n"/>
       <c r="F20" s="7" t="n"/>
-      <c r="G20" s="6" t="n"/>
+      <c r="G20" s="7" t="n"/>
       <c r="H20" s="6" t="n"/>
       <c r="I20" s="6" t="n"/>
-      <c r="J20" s="7" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="6" t="n"/>
       <c r="F21" s="7" t="n"/>
-      <c r="G21" s="6" t="n"/>
+      <c r="G21" s="7" t="n"/>
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="6" t="n"/>
-      <c r="J21" s="7" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="6" t="n"/>
       <c r="F22" s="7" t="n"/>
-      <c r="G22" s="6" t="n"/>
+      <c r="G22" s="7" t="n"/>
       <c r="H22" s="6" t="n"/>
       <c r="I22" s="6" t="n"/>
-      <c r="J22" s="7" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="6" t="n"/>
       <c r="F23" s="7" t="n"/>
-      <c r="G23" s="6" t="n"/>
+      <c r="G23" s="7" t="n"/>
       <c r="H23" s="6" t="n"/>
       <c r="I23" s="6" t="n"/>
-      <c r="J23" s="7" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="6" t="n"/>
       <c r="F24" s="7" t="n"/>
-      <c r="G24" s="6" t="n"/>
+      <c r="G24" s="7" t="n"/>
       <c r="H24" s="6" t="n"/>
       <c r="I24" s="6" t="n"/>
-      <c r="J24" s="7" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="6" t="n"/>
       <c r="F25" s="7" t="n"/>
-      <c r="G25" s="6" t="n"/>
+      <c r="G25" s="7" t="n"/>
       <c r="H25" s="6" t="n"/>
       <c r="I25" s="6" t="n"/>
-      <c r="J25" s="7" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="6" t="n"/>
       <c r="F26" s="7" t="n"/>
-      <c r="G26" s="6" t="n"/>
+      <c r="G26" s="7" t="n"/>
       <c r="H26" s="6" t="n"/>
       <c r="I26" s="6" t="n"/>
-      <c r="J26" s="7" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="6" t="n"/>
       <c r="F27" s="7" t="n"/>
-      <c r="G27" s="6" t="n"/>
+      <c r="G27" s="7" t="n"/>
       <c r="H27" s="6" t="n"/>
       <c r="I27" s="6" t="n"/>
-      <c r="J27" s="7" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
       <c r="B28" s="6" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="6" t="n"/>
       <c r="F28" s="7" t="n"/>
-      <c r="G28" s="6" t="n"/>
+      <c r="G28" s="7" t="n"/>
       <c r="H28" s="6" t="n"/>
       <c r="I28" s="6" t="n"/>
-      <c r="J28" s="7" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
       <c r="B29" s="6" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="6" t="n"/>
       <c r="F29" s="7" t="n"/>
-      <c r="G29" s="6" t="n"/>
+      <c r="G29" s="7" t="n"/>
       <c r="H29" s="6" t="n"/>
       <c r="I29" s="6" t="n"/>
-      <c r="J29" s="7" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
       <c r="B30" s="6" t="n"/>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="6" t="n"/>
       <c r="F30" s="7" t="n"/>
-      <c r="G30" s="6" t="n"/>
+      <c r="G30" s="7" t="n"/>
       <c r="H30" s="6" t="n"/>
       <c r="I30" s="6" t="n"/>
-      <c r="J30" s="7" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="6" t="n"/>
       <c r="F31" s="7" t="n"/>
-      <c r="G31" s="6" t="n"/>
+      <c r="G31" s="7" t="n"/>
       <c r="H31" s="6" t="n"/>
       <c r="I31" s="6" t="n"/>
-      <c r="J31" s="7" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="6" t="n"/>
       <c r="F32" s="7" t="n"/>
-      <c r="G32" s="6" t="n"/>
+      <c r="G32" s="7" t="n"/>
       <c r="H32" s="6" t="n"/>
       <c r="I32" s="6" t="n"/>
-      <c r="J32" s="7" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
       <c r="B33" s="6" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="6" t="n"/>
       <c r="F33" s="7" t="n"/>
-      <c r="G33" s="6" t="n"/>
+      <c r="G33" s="7" t="n"/>
       <c r="H33" s="6" t="n"/>
       <c r="I33" s="6" t="n"/>
-      <c r="J33" s="7" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="6" t="n"/>
       <c r="F34" s="7" t="n"/>
-      <c r="G34" s="6" t="n"/>
+      <c r="G34" s="7" t="n"/>
       <c r="H34" s="6" t="n"/>
       <c r="I34" s="6" t="n"/>
-      <c r="J34" s="7" t="n"/>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
       <c r="B35" s="6" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="6" t="n"/>
       <c r="F35" s="7" t="n"/>
-      <c r="G35" s="6" t="n"/>
+      <c r="G35" s="7" t="n"/>
       <c r="H35" s="6" t="n"/>
       <c r="I35" s="6" t="n"/>
-      <c r="J35" s="7" t="n"/>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="6" t="n"/>
-      <c r="E36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="6" t="n"/>
       <c r="F36" s="7" t="n"/>
-      <c r="G36" s="6" t="n"/>
+      <c r="G36" s="7" t="n"/>
       <c r="H36" s="6" t="n"/>
       <c r="I36" s="6" t="n"/>
-      <c r="J36" s="7" t="n"/>
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
       <c r="B37" s="6" t="n"/>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="6" t="n"/>
       <c r="F37" s="7" t="n"/>
-      <c r="G37" s="6" t="n"/>
+      <c r="G37" s="7" t="n"/>
       <c r="H37" s="6" t="n"/>
       <c r="I37" s="6" t="n"/>
-      <c r="J37" s="7" t="n"/>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
       <c r="B38" s="6" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="6" t="n"/>
       <c r="F38" s="7" t="n"/>
-      <c r="G38" s="6" t="n"/>
+      <c r="G38" s="7" t="n"/>
       <c r="H38" s="6" t="n"/>
       <c r="I38" s="6" t="n"/>
-      <c r="J38" s="7" t="n"/>
+      <c r="J38" s="6" t="n"/>
+      <c r="K38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
       <c r="B39" s="6" t="n"/>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="6" t="n"/>
-      <c r="E39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="6" t="n"/>
       <c r="F39" s="7" t="n"/>
-      <c r="G39" s="6" t="n"/>
+      <c r="G39" s="7" t="n"/>
       <c r="H39" s="6" t="n"/>
       <c r="I39" s="6" t="n"/>
-      <c r="J39" s="7" t="n"/>
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
       <c r="B40" s="6" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="6" t="n"/>
       <c r="F40" s="7" t="n"/>
-      <c r="G40" s="6" t="n"/>
+      <c r="G40" s="7" t="n"/>
       <c r="H40" s="6" t="n"/>
       <c r="I40" s="6" t="n"/>
-      <c r="J40" s="7" t="n"/>
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
       <c r="B41" s="6" t="n"/>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="6" t="n"/>
       <c r="F41" s="7" t="n"/>
-      <c r="G41" s="6" t="n"/>
+      <c r="G41" s="7" t="n"/>
       <c r="H41" s="6" t="n"/>
       <c r="I41" s="6" t="n"/>
-      <c r="J41" s="7" t="n"/>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="6" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="6" t="n"/>
       <c r="F42" s="7" t="n"/>
-      <c r="G42" s="6" t="n"/>
+      <c r="G42" s="7" t="n"/>
       <c r="H42" s="6" t="n"/>
       <c r="I42" s="6" t="n"/>
-      <c r="J42" s="7" t="n"/>
+      <c r="J42" s="6" t="n"/>
+      <c r="K42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
       <c r="B43" s="6" t="n"/>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="6" t="n"/>
       <c r="F43" s="7" t="n"/>
-      <c r="G43" s="6" t="n"/>
+      <c r="G43" s="7" t="n"/>
       <c r="H43" s="6" t="n"/>
       <c r="I43" s="6" t="n"/>
-      <c r="J43" s="7" t="n"/>
+      <c r="J43" s="6" t="n"/>
+      <c r="K43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
       <c r="B44" s="6" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="7" t="n"/>
+      <c r="D44" s="7" t="n"/>
+      <c r="E44" s="6" t="n"/>
       <c r="F44" s="7" t="n"/>
-      <c r="G44" s="6" t="n"/>
+      <c r="G44" s="7" t="n"/>
       <c r="H44" s="6" t="n"/>
       <c r="I44" s="6" t="n"/>
-      <c r="J44" s="7" t="n"/>
+      <c r="J44" s="6" t="n"/>
+      <c r="K44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
       <c r="B45" s="6" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="6" t="n"/>
-      <c r="E45" s="7" t="n"/>
+      <c r="D45" s="7" t="n"/>
+      <c r="E45" s="6" t="n"/>
       <c r="F45" s="7" t="n"/>
-      <c r="G45" s="6" t="n"/>
+      <c r="G45" s="7" t="n"/>
       <c r="H45" s="6" t="n"/>
       <c r="I45" s="6" t="n"/>
-      <c r="J45" s="7" t="n"/>
+      <c r="J45" s="6" t="n"/>
+      <c r="K45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
       <c r="B46" s="6" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="7" t="n"/>
+      <c r="D46" s="7" t="n"/>
+      <c r="E46" s="6" t="n"/>
       <c r="F46" s="7" t="n"/>
-      <c r="G46" s="6" t="n"/>
+      <c r="G46" s="7" t="n"/>
       <c r="H46" s="6" t="n"/>
       <c r="I46" s="6" t="n"/>
-      <c r="J46" s="7" t="n"/>
+      <c r="J46" s="6" t="n"/>
+      <c r="K46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
       <c r="B47" s="6" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="6" t="n"/>
       <c r="F47" s="7" t="n"/>
-      <c r="G47" s="6" t="n"/>
+      <c r="G47" s="7" t="n"/>
       <c r="H47" s="6" t="n"/>
       <c r="I47" s="6" t="n"/>
-      <c r="J47" s="7" t="n"/>
+      <c r="J47" s="6" t="n"/>
+      <c r="K47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
       <c r="B48" s="6" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="6" t="n"/>
-      <c r="E48" s="7" t="n"/>
+      <c r="D48" s="7" t="n"/>
+      <c r="E48" s="6" t="n"/>
       <c r="F48" s="7" t="n"/>
-      <c r="G48" s="6" t="n"/>
+      <c r="G48" s="7" t="n"/>
       <c r="H48" s="6" t="n"/>
       <c r="I48" s="6" t="n"/>
-      <c r="J48" s="7" t="n"/>
+      <c r="J48" s="6" t="n"/>
+      <c r="K48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="6" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="6" t="n"/>
-      <c r="E49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
+      <c r="E49" s="6" t="n"/>
       <c r="F49" s="7" t="n"/>
-      <c r="G49" s="6" t="n"/>
+      <c r="G49" s="7" t="n"/>
       <c r="H49" s="6" t="n"/>
       <c r="I49" s="6" t="n"/>
-      <c r="J49" s="7" t="n"/>
+      <c r="J49" s="6" t="n"/>
+      <c r="K49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
       <c r="B50" s="6" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="7" t="n"/>
+      <c r="D50" s="7" t="n"/>
+      <c r="E50" s="6" t="n"/>
       <c r="F50" s="7" t="n"/>
-      <c r="G50" s="6" t="n"/>
+      <c r="G50" s="7" t="n"/>
       <c r="H50" s="6" t="n"/>
       <c r="I50" s="6" t="n"/>
-      <c r="J50" s="7" t="n"/>
+      <c r="J50" s="6" t="n"/>
+      <c r="K50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
       <c r="B51" s="6" t="n"/>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
+      <c r="E51" s="6" t="n"/>
       <c r="F51" s="7" t="n"/>
-      <c r="G51" s="6" t="n"/>
+      <c r="G51" s="7" t="n"/>
       <c r="H51" s="6" t="n"/>
       <c r="I51" s="6" t="n"/>
-      <c r="J51" s="7" t="n"/>
+      <c r="J51" s="6" t="n"/>
+      <c r="K51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="6" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="6" t="n"/>
-      <c r="E52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
+      <c r="E52" s="6" t="n"/>
       <c r="F52" s="7" t="n"/>
-      <c r="G52" s="6" t="n"/>
+      <c r="G52" s="7" t="n"/>
       <c r="H52" s="6" t="n"/>
       <c r="I52" s="6" t="n"/>
-      <c r="J52" s="7" t="n"/>
+      <c r="J52" s="6" t="n"/>
+      <c r="K52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="6" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="7" t="n"/>
+      <c r="D53" s="7" t="n"/>
+      <c r="E53" s="6" t="n"/>
       <c r="F53" s="7" t="n"/>
-      <c r="G53" s="6" t="n"/>
+      <c r="G53" s="7" t="n"/>
       <c r="H53" s="6" t="n"/>
       <c r="I53" s="6" t="n"/>
-      <c r="J53" s="7" t="n"/>
+      <c r="J53" s="6" t="n"/>
+      <c r="K53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="6" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="6" t="n"/>
-      <c r="E54" s="7" t="n"/>
+      <c r="D54" s="7" t="n"/>
+      <c r="E54" s="6" t="n"/>
       <c r="F54" s="7" t="n"/>
-      <c r="G54" s="6" t="n"/>
+      <c r="G54" s="7" t="n"/>
       <c r="H54" s="6" t="n"/>
       <c r="I54" s="6" t="n"/>
-      <c r="J54" s="7" t="n"/>
+      <c r="J54" s="6" t="n"/>
+      <c r="K54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="6" t="n"/>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="6" t="n"/>
-      <c r="E55" s="7" t="n"/>
+      <c r="D55" s="7" t="n"/>
+      <c r="E55" s="6" t="n"/>
       <c r="F55" s="7" t="n"/>
-      <c r="G55" s="6" t="n"/>
+      <c r="G55" s="7" t="n"/>
       <c r="H55" s="6" t="n"/>
       <c r="I55" s="6" t="n"/>
-      <c r="J55" s="7" t="n"/>
+      <c r="J55" s="6" t="n"/>
+      <c r="K55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="6" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="6" t="n"/>
-      <c r="E56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
+      <c r="E56" s="6" t="n"/>
       <c r="F56" s="7" t="n"/>
-      <c r="G56" s="6" t="n"/>
+      <c r="G56" s="7" t="n"/>
       <c r="H56" s="6" t="n"/>
       <c r="I56" s="6" t="n"/>
-      <c r="J56" s="7" t="n"/>
+      <c r="J56" s="6" t="n"/>
+      <c r="K56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="6" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="6" t="n"/>
-      <c r="E57" s="7" t="n"/>
+      <c r="D57" s="7" t="n"/>
+      <c r="E57" s="6" t="n"/>
       <c r="F57" s="7" t="n"/>
-      <c r="G57" s="6" t="n"/>
+      <c r="G57" s="7" t="n"/>
       <c r="H57" s="6" t="n"/>
       <c r="I57" s="6" t="n"/>
-      <c r="J57" s="7" t="n"/>
+      <c r="J57" s="6" t="n"/>
+      <c r="K57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
       <c r="B58" s="6" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="6" t="n"/>
-      <c r="E58" s="7" t="n"/>
+      <c r="D58" s="7" t="n"/>
+      <c r="E58" s="6" t="n"/>
       <c r="F58" s="7" t="n"/>
-      <c r="G58" s="6" t="n"/>
+      <c r="G58" s="7" t="n"/>
       <c r="H58" s="6" t="n"/>
       <c r="I58" s="6" t="n"/>
-      <c r="J58" s="7" t="n"/>
+      <c r="J58" s="6" t="n"/>
+      <c r="K58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
       <c r="B59" s="6" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="7" t="n"/>
+      <c r="D59" s="7" t="n"/>
+      <c r="E59" s="6" t="n"/>
       <c r="F59" s="7" t="n"/>
-      <c r="G59" s="6" t="n"/>
+      <c r="G59" s="7" t="n"/>
       <c r="H59" s="6" t="n"/>
       <c r="I59" s="6" t="n"/>
-      <c r="J59" s="7" t="n"/>
+      <c r="J59" s="6" t="n"/>
+      <c r="K59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
       <c r="B60" s="6" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="6" t="n"/>
-      <c r="E60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="6" t="n"/>
       <c r="F60" s="7" t="n"/>
-      <c r="G60" s="6" t="n"/>
+      <c r="G60" s="7" t="n"/>
       <c r="H60" s="6" t="n"/>
       <c r="I60" s="6" t="n"/>
-      <c r="J60" s="7" t="n"/>
+      <c r="J60" s="6" t="n"/>
+      <c r="K60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n"/>
       <c r="B61" s="6" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="6" t="n"/>
-      <c r="E61" s="7" t="n"/>
+      <c r="D61" s="7" t="n"/>
+      <c r="E61" s="6" t="n"/>
       <c r="F61" s="7" t="n"/>
-      <c r="G61" s="6" t="n"/>
+      <c r="G61" s="7" t="n"/>
       <c r="H61" s="6" t="n"/>
       <c r="I61" s="6" t="n"/>
-      <c r="J61" s="7" t="n"/>
+      <c r="J61" s="6" t="n"/>
+      <c r="K61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n"/>
       <c r="B62" s="6" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="7" t="n"/>
+      <c r="D62" s="7" t="n"/>
+      <c r="E62" s="6" t="n"/>
       <c r="F62" s="7" t="n"/>
-      <c r="G62" s="6" t="n"/>
+      <c r="G62" s="7" t="n"/>
       <c r="H62" s="6" t="n"/>
       <c r="I62" s="6" t="n"/>
-      <c r="J62" s="7" t="n"/>
+      <c r="J62" s="6" t="n"/>
+      <c r="K62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n"/>
       <c r="B63" s="6" t="n"/>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="6" t="n"/>
-      <c r="E63" s="7" t="n"/>
+      <c r="D63" s="7" t="n"/>
+      <c r="E63" s="6" t="n"/>
       <c r="F63" s="7" t="n"/>
-      <c r="G63" s="6" t="n"/>
+      <c r="G63" s="7" t="n"/>
       <c r="H63" s="6" t="n"/>
       <c r="I63" s="6" t="n"/>
-      <c r="J63" s="7" t="n"/>
+      <c r="J63" s="6" t="n"/>
+      <c r="K63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
       <c r="B64" s="6" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="6" t="n"/>
-      <c r="E64" s="7" t="n"/>
+      <c r="D64" s="7" t="n"/>
+      <c r="E64" s="6" t="n"/>
       <c r="F64" s="7" t="n"/>
-      <c r="G64" s="6" t="n"/>
+      <c r="G64" s="7" t="n"/>
       <c r="H64" s="6" t="n"/>
       <c r="I64" s="6" t="n"/>
-      <c r="J64" s="7" t="n"/>
+      <c r="J64" s="6" t="n"/>
+      <c r="K64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n"/>
       <c r="B65" s="6" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="6" t="n"/>
-      <c r="E65" s="7" t="n"/>
+      <c r="D65" s="7" t="n"/>
+      <c r="E65" s="6" t="n"/>
       <c r="F65" s="7" t="n"/>
-      <c r="G65" s="6" t="n"/>
+      <c r="G65" s="7" t="n"/>
       <c r="H65" s="6" t="n"/>
       <c r="I65" s="6" t="n"/>
-      <c r="J65" s="7" t="n"/>
+      <c r="J65" s="6" t="n"/>
+      <c r="K65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n"/>
       <c r="B66" s="6" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="6" t="n"/>
-      <c r="E66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="6" t="n"/>
       <c r="F66" s="7" t="n"/>
-      <c r="G66" s="6" t="n"/>
+      <c r="G66" s="7" t="n"/>
       <c r="H66" s="6" t="n"/>
       <c r="I66" s="6" t="n"/>
-      <c r="J66" s="7" t="n"/>
+      <c r="J66" s="6" t="n"/>
+      <c r="K66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n"/>
       <c r="B67" s="6" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="6" t="n"/>
-      <c r="E67" s="7" t="n"/>
+      <c r="D67" s="7" t="n"/>
+      <c r="E67" s="6" t="n"/>
       <c r="F67" s="7" t="n"/>
-      <c r="G67" s="6" t="n"/>
+      <c r="G67" s="7" t="n"/>
       <c r="H67" s="6" t="n"/>
       <c r="I67" s="6" t="n"/>
-      <c r="J67" s="7" t="n"/>
+      <c r="J67" s="6" t="n"/>
+      <c r="K67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
       <c r="B68" s="6" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="6" t="n"/>
-      <c r="E68" s="7" t="n"/>
+      <c r="D68" s="7" t="n"/>
+      <c r="E68" s="6" t="n"/>
       <c r="F68" s="7" t="n"/>
-      <c r="G68" s="6" t="n"/>
+      <c r="G68" s="7" t="n"/>
       <c r="H68" s="6" t="n"/>
       <c r="I68" s="6" t="n"/>
-      <c r="J68" s="7" t="n"/>
+      <c r="J68" s="6" t="n"/>
+      <c r="K68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n"/>
       <c r="B69" s="6" t="n"/>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="6" t="n"/>
-      <c r="E69" s="7" t="n"/>
+      <c r="D69" s="7" t="n"/>
+      <c r="E69" s="6" t="n"/>
       <c r="F69" s="7" t="n"/>
-      <c r="G69" s="6" t="n"/>
+      <c r="G69" s="7" t="n"/>
       <c r="H69" s="6" t="n"/>
       <c r="I69" s="6" t="n"/>
-      <c r="J69" s="7" t="n"/>
+      <c r="J69" s="6" t="n"/>
+      <c r="K69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n"/>
       <c r="B70" s="6" t="n"/>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="6" t="n"/>
-      <c r="E70" s="7" t="n"/>
+      <c r="D70" s="7" t="n"/>
+      <c r="E70" s="6" t="n"/>
       <c r="F70" s="7" t="n"/>
-      <c r="G70" s="6" t="n"/>
+      <c r="G70" s="7" t="n"/>
       <c r="H70" s="6" t="n"/>
       <c r="I70" s="6" t="n"/>
-      <c r="J70" s="7" t="n"/>
+      <c r="J70" s="6" t="n"/>
+      <c r="K70" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B2:J2"/>
+  <mergeCells count="7">
+    <mergeCell ref="B8:K8"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B5:K5"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="A11:A70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"수업자동화,업무자동화"</formula1>
     </dataValidation>
-    <dataValidation sqref="I11:I70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J11:J70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"확정,검토 중,초안,가안,보류,재검토"</formula1>
     </dataValidation>
   </dataValidations>

--- a/엑셀양식/최종목차_탭_양식.xlsx
+++ b/엑셀양식/최종목차_탭_양식.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -498,6 +498,7 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -558,163 +559,155 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>세부 내용</t>
+          <t>대체 가능</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>꼭지 아래에 보일 항목. 한 칸 안에서 줄을 바꿔(Alt+Enter) 하나씩 적기</t>
+          <t>재검토 행에만: 수준을 맞추면 어떤 가안 꼭지를 대신할 수 있는지</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>바탕 아이디어 번호</t>
+          <t>세부 내용</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>같은 권의 아이디어 번호를 쉼표로 (예: 21, 22). 다른 권 아이디어는 '수업 14', '업무 7'처럼</t>
+          <t>꼭지 아래에 보일 항목. 한 칸 안에서 줄을 바꿔(Alt+Enter) 하나씩 적기</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>바탕 아이디어 번호</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>같은 권의 아이디어 번호를 쉼표로 (예: 21, 22). 다른 권 아이디어는 '수업 14', '업무 7'처럼</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>확정 / 검토 중 / 초안 / 가안 / 보류 / 재검토 — ‘재검토’ 행은 목차에서 빠지고 ‘재검토 아이디어’에 비고(이유)와 함께 표시</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>권</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>파트 번호</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>파트 제목</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>파트 설명</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>꼭지 번호</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>꼭지 제목</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>세부 내용</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>바탕 아이디어 번호</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>저자</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>대체 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>프롬프트 기초</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>프롬프트가 결과를 좌우한다
 마크다운 기초</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>검토 중</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="7" t="n"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -728,6 +721,7 @@
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -741,6 +735,7 @@
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="6" t="n"/>
       <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -754,6 +749,7 @@
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -767,6 +763,7 @@
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="6" t="n"/>
       <c r="K16" s="7" t="n"/>
+      <c r="L16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -780,6 +777,7 @@
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -793,6 +791,7 @@
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="n"/>
       <c r="K18" s="7" t="n"/>
+      <c r="L18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -806,6 +805,7 @@
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -819,6 +819,7 @@
       <c r="I20" s="6" t="n"/>
       <c r="J20" s="6" t="n"/>
       <c r="K20" s="7" t="n"/>
+      <c r="L20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -832,6 +833,7 @@
       <c r="I21" s="6" t="n"/>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="7" t="n"/>
+      <c r="L21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -845,6 +847,7 @@
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="7" t="n"/>
+      <c r="L22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -858,6 +861,7 @@
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="7" t="n"/>
+      <c r="L23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -871,6 +875,7 @@
       <c r="I24" s="6" t="n"/>
       <c r="J24" s="6" t="n"/>
       <c r="K24" s="7" t="n"/>
+      <c r="L24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -884,6 +889,7 @@
       <c r="I25" s="6" t="n"/>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="7" t="n"/>
+      <c r="L25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -897,6 +903,7 @@
       <c r="I26" s="6" t="n"/>
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="7" t="n"/>
+      <c r="L26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -910,6 +917,7 @@
       <c r="I27" s="6" t="n"/>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="7" t="n"/>
+      <c r="L27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -923,6 +931,7 @@
       <c r="I28" s="6" t="n"/>
       <c r="J28" s="6" t="n"/>
       <c r="K28" s="7" t="n"/>
+      <c r="L28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -936,6 +945,7 @@
       <c r="I29" s="6" t="n"/>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="7" t="n"/>
+      <c r="L29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -949,6 +959,7 @@
       <c r="I30" s="6" t="n"/>
       <c r="J30" s="6" t="n"/>
       <c r="K30" s="7" t="n"/>
+      <c r="L30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -962,6 +973,7 @@
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="7" t="n"/>
+      <c r="L31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -975,6 +987,7 @@
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="7" t="n"/>
+      <c r="L32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -988,6 +1001,7 @@
       <c r="I33" s="6" t="n"/>
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -1001,6 +1015,7 @@
       <c r="I34" s="6" t="n"/>
       <c r="J34" s="6" t="n"/>
       <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -1014,6 +1029,7 @@
       <c r="I35" s="6" t="n"/>
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -1027,6 +1043,7 @@
       <c r="I36" s="6" t="n"/>
       <c r="J36" s="6" t="n"/>
       <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -1040,6 +1057,7 @@
       <c r="I37" s="6" t="n"/>
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -1053,6 +1071,7 @@
       <c r="I38" s="6" t="n"/>
       <c r="J38" s="6" t="n"/>
       <c r="K38" s="7" t="n"/>
+      <c r="L38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -1066,6 +1085,7 @@
       <c r="I39" s="6" t="n"/>
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="7" t="n"/>
+      <c r="L39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -1079,6 +1099,7 @@
       <c r="I40" s="6" t="n"/>
       <c r="J40" s="6" t="n"/>
       <c r="K40" s="7" t="n"/>
+      <c r="L40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -1092,6 +1113,7 @@
       <c r="I41" s="6" t="n"/>
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="7" t="n"/>
+      <c r="L41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -1105,6 +1127,7 @@
       <c r="I42" s="6" t="n"/>
       <c r="J42" s="6" t="n"/>
       <c r="K42" s="7" t="n"/>
+      <c r="L42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -1118,6 +1141,7 @@
       <c r="I43" s="6" t="n"/>
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="7" t="n"/>
+      <c r="L43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -1131,6 +1155,7 @@
       <c r="I44" s="6" t="n"/>
       <c r="J44" s="6" t="n"/>
       <c r="K44" s="7" t="n"/>
+      <c r="L44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -1144,6 +1169,7 @@
       <c r="I45" s="6" t="n"/>
       <c r="J45" s="6" t="n"/>
       <c r="K45" s="7" t="n"/>
+      <c r="L45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -1157,6 +1183,7 @@
       <c r="I46" s="6" t="n"/>
       <c r="J46" s="6" t="n"/>
       <c r="K46" s="7" t="n"/>
+      <c r="L46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -1170,6 +1197,7 @@
       <c r="I47" s="6" t="n"/>
       <c r="J47" s="6" t="n"/>
       <c r="K47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -1183,6 +1211,7 @@
       <c r="I48" s="6" t="n"/>
       <c r="J48" s="6" t="n"/>
       <c r="K48" s="7" t="n"/>
+      <c r="L48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -1196,6 +1225,7 @@
       <c r="I49" s="6" t="n"/>
       <c r="J49" s="6" t="n"/>
       <c r="K49" s="7" t="n"/>
+      <c r="L49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -1209,6 +1239,7 @@
       <c r="I50" s="6" t="n"/>
       <c r="J50" s="6" t="n"/>
       <c r="K50" s="7" t="n"/>
+      <c r="L50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -1222,6 +1253,7 @@
       <c r="I51" s="6" t="n"/>
       <c r="J51" s="6" t="n"/>
       <c r="K51" s="7" t="n"/>
+      <c r="L51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -1235,6 +1267,7 @@
       <c r="I52" s="6" t="n"/>
       <c r="J52" s="6" t="n"/>
       <c r="K52" s="7" t="n"/>
+      <c r="L52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -1248,6 +1281,7 @@
       <c r="I53" s="6" t="n"/>
       <c r="J53" s="6" t="n"/>
       <c r="K53" s="7" t="n"/>
+      <c r="L53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -1261,6 +1295,7 @@
       <c r="I54" s="6" t="n"/>
       <c r="J54" s="6" t="n"/>
       <c r="K54" s="7" t="n"/>
+      <c r="L54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -1274,6 +1309,7 @@
       <c r="I55" s="6" t="n"/>
       <c r="J55" s="6" t="n"/>
       <c r="K55" s="7" t="n"/>
+      <c r="L55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -1287,6 +1323,7 @@
       <c r="I56" s="6" t="n"/>
       <c r="J56" s="6" t="n"/>
       <c r="K56" s="7" t="n"/>
+      <c r="L56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -1300,6 +1337,7 @@
       <c r="I57" s="6" t="n"/>
       <c r="J57" s="6" t="n"/>
       <c r="K57" s="7" t="n"/>
+      <c r="L57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -1313,6 +1351,7 @@
       <c r="I58" s="6" t="n"/>
       <c r="J58" s="6" t="n"/>
       <c r="K58" s="7" t="n"/>
+      <c r="L58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -1326,6 +1365,7 @@
       <c r="I59" s="6" t="n"/>
       <c r="J59" s="6" t="n"/>
       <c r="K59" s="7" t="n"/>
+      <c r="L59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -1339,6 +1379,7 @@
       <c r="I60" s="6" t="n"/>
       <c r="J60" s="6" t="n"/>
       <c r="K60" s="7" t="n"/>
+      <c r="L60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n"/>
@@ -1352,6 +1393,7 @@
       <c r="I61" s="6" t="n"/>
       <c r="J61" s="6" t="n"/>
       <c r="K61" s="7" t="n"/>
+      <c r="L61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n"/>
@@ -1365,6 +1407,7 @@
       <c r="I62" s="6" t="n"/>
       <c r="J62" s="6" t="n"/>
       <c r="K62" s="7" t="n"/>
+      <c r="L62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n"/>
@@ -1378,6 +1421,7 @@
       <c r="I63" s="6" t="n"/>
       <c r="J63" s="6" t="n"/>
       <c r="K63" s="7" t="n"/>
+      <c r="L63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -1391,6 +1435,7 @@
       <c r="I64" s="6" t="n"/>
       <c r="J64" s="6" t="n"/>
       <c r="K64" s="7" t="n"/>
+      <c r="L64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n"/>
@@ -1404,6 +1449,7 @@
       <c r="I65" s="6" t="n"/>
       <c r="J65" s="6" t="n"/>
       <c r="K65" s="7" t="n"/>
+      <c r="L65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n"/>
@@ -1417,6 +1463,7 @@
       <c r="I66" s="6" t="n"/>
       <c r="J66" s="6" t="n"/>
       <c r="K66" s="7" t="n"/>
+      <c r="L66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n"/>
@@ -1430,6 +1477,7 @@
       <c r="I67" s="6" t="n"/>
       <c r="J67" s="6" t="n"/>
       <c r="K67" s="7" t="n"/>
+      <c r="L67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -1443,6 +1491,7 @@
       <c r="I68" s="6" t="n"/>
       <c r="J68" s="6" t="n"/>
       <c r="K68" s="7" t="n"/>
+      <c r="L68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n"/>
@@ -1456,6 +1505,7 @@
       <c r="I69" s="6" t="n"/>
       <c r="J69" s="6" t="n"/>
       <c r="K69" s="7" t="n"/>
+      <c r="L69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n"/>
@@ -1469,22 +1519,52 @@
       <c r="I70" s="6" t="n"/>
       <c r="J70" s="6" t="n"/>
       <c r="K70" s="7" t="n"/>
+      <c r="L70" s="7" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n"/>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="7" t="n"/>
+      <c r="G71" s="7" t="n"/>
+      <c r="H71" s="6" t="n"/>
+      <c r="I71" s="6" t="n"/>
+      <c r="J71" s="6" t="n"/>
+      <c r="K71" s="7" t="n"/>
+      <c r="L71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="n"/>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="7" t="n"/>
+      <c r="E72" s="6" t="n"/>
+      <c r="F72" s="7" t="n"/>
+      <c r="G72" s="7" t="n"/>
+      <c r="H72" s="6" t="n"/>
+      <c r="I72" s="6" t="n"/>
+      <c r="J72" s="6" t="n"/>
+      <c r="K72" s="7" t="n"/>
+      <c r="L72" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B8:K8"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B7:K7"/>
-    <mergeCell ref="B6:K6"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B5:K5"/>
+  <mergeCells count="8">
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B6:L6"/>
+    <mergeCell ref="B7:L7"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="B9:L9"/>
+    <mergeCell ref="B8:L8"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A11:A70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A13:A72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"수업자동화,업무자동화"</formula1>
     </dataValidation>
-    <dataValidation sqref="J11:J70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J13:J72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"확정,검토 중,초안,가안,보류,재검토"</formula1>
     </dataValidation>
   </dataValidations>
